--- a/artfynd/A 23984-2022 artfynd.xlsx
+++ b/artfynd/A 23984-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23984-2022 artfynd.xlsx
+++ b/artfynd/A 23984-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96362185</v>
+        <v>119299688</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Laxöringtjärnarna, Hls</t>
+          <t>S Laxöringstjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560161.3868687096</v>
+        <v>560180</v>
       </c>
       <c r="R2" t="n">
-        <v>6869159.996834037</v>
+        <v>6869037</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Högstubbe.</t>
+          <t>Gammal tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96362484</v>
+        <v>96362520</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560318.9099312205</v>
+        <v>560386</v>
       </c>
       <c r="R3" t="n">
-        <v>6869102.065751534</v>
+        <v>6869130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,24 +853,14 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>På två granlågor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96362520</v>
+        <v>119300157</v>
       </c>
       <c r="B4" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,14 +922,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laxöringtjärnarna, Hls</t>
+          <t>S Laxöringstjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560385.3499950048</v>
+        <v>560203</v>
       </c>
       <c r="R4" t="n">
-        <v>6869130.072072711</v>
+        <v>6869100</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,27 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På två granlågor.</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96362551</v>
+        <v>119299449</v>
       </c>
       <c r="B5" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,14 +1023,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxöringtjärnarna, Hls</t>
+          <t>N Laxöringstjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560377.3974278826</v>
+        <v>560067</v>
       </c>
       <c r="R5" t="n">
-        <v>6869126.636305572</v>
+        <v>6868823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,27 +1057,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Granbark</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96362203</v>
+        <v>119299894</v>
       </c>
       <c r="B6" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,14 +1124,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Laxöringtjärnarna, Hls</t>
+          <t>S Laxöringstjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560114.6482726487</v>
+        <v>560442</v>
       </c>
       <c r="R6" t="n">
-        <v>6869110.691641307</v>
+        <v>6869019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,27 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd i området på tall o gran.</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,12 +1194,7 @@
         <v>96362564</v>
       </c>
       <c r="B7" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560464.508801972</v>
+        <v>560465</v>
       </c>
       <c r="R7" t="n">
-        <v>6869131.947325914</v>
+        <v>6869132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,19 +1262,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1401,37 +1297,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96362269</v>
+        <v>97495431</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1440,14 +1331,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Laxöringtjärnarna, Hls</t>
+          <t>Laxöringstjärnanra, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560109.2721332685</v>
+        <v>560379</v>
       </c>
       <c r="R8" t="n">
-        <v>6868934.557505616</v>
+        <v>6869135</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,22 +1365,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,15 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96362326</v>
+        <v>96362720</v>
       </c>
       <c r="B9" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1560,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560188.5796265161</v>
+        <v>560478</v>
       </c>
       <c r="R9" t="n">
-        <v>6868901.596510872</v>
+        <v>6869171</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,24 +1474,14 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Torrgran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,37 +1509,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96362340</v>
+        <v>119300124</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1677,14 +1543,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Laxöringtjärnarna, Hls</t>
+          <t>S Laxöringstjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560270.5008643693</v>
+        <v>560293</v>
       </c>
       <c r="R10" t="n">
-        <v>6869067.319294408</v>
+        <v>6869024</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,27 +1577,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>På gammal tallåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,53 +1615,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97495431</v>
+        <v>119299724</v>
       </c>
       <c r="B11" t="n">
-        <v>89588</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1106</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Laxöringstjärnanra, Hls</t>
+          <t>S Laxöringstjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560379.6117694743</v>
+        <v>560196</v>
       </c>
       <c r="R11" t="n">
-        <v>6869134.677122139</v>
+        <v>6869120</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,27 +1684,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,54 +1717,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119299739</v>
+        <v>96362269</v>
       </c>
       <c r="B12" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>S Laxöringstjärnarna, Hls</t>
+          <t>Laxöringtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560408</v>
+        <v>560109</v>
       </c>
       <c r="R12" t="n">
-        <v>6869105</v>
+        <v>6868935</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,12 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,15 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119300082</v>
+        <v>119299481</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2026,14 +1852,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>S Laxöringstjärnarna, Hls</t>
+          <t>N Laxöringstjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560269</v>
+        <v>560077</v>
       </c>
       <c r="R13" t="n">
-        <v>6869053</v>
+        <v>6868900</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,11 +1892,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2098,43 +1919,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119300035</v>
+        <v>119299505</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2142,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560298</v>
+        <v>560084</v>
       </c>
       <c r="R14" t="n">
-        <v>6869055</v>
+        <v>6868936</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,11 +1993,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter c:a 1m2</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,43 +2020,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119299941</v>
+        <v>119299528</v>
       </c>
       <c r="B15" t="n">
-        <v>97941</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2254,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560389</v>
+        <v>560111</v>
       </c>
       <c r="R15" t="n">
-        <v>6869030</v>
+        <v>6868935</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2317,15 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119299888</v>
+        <v>119299658</v>
       </c>
       <c r="B16" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,21 +2132,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2360,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560451</v>
+        <v>560118</v>
       </c>
       <c r="R16" t="n">
-        <v>6869026</v>
+        <v>6868997</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,11 +2195,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Brandhögstubbe tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,37 +2222,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119299968</v>
+        <v>119299642</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2471,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560384</v>
+        <v>560157</v>
       </c>
       <c r="R17" t="n">
-        <v>6869021</v>
+        <v>6868939</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,7 +2300,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På mkt gammal sälg.</t>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,15 +2328,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119300075</v>
+        <v>119299707</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,27 +2339,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2583,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560283</v>
+        <v>560194</v>
       </c>
       <c r="R18" t="n">
-        <v>6869048</v>
+        <v>6869042</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,7 +2406,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med bladrosetter c:a 1m2</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,37 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119299528</v>
+        <v>119299733</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2694,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560111</v>
+        <v>560426</v>
       </c>
       <c r="R19" t="n">
-        <v>6868935</v>
+        <v>6869106</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,6 +2508,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Tallstam</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,37 +2540,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119299658</v>
+        <v>119299792</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2800,10 +2578,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560118</v>
+        <v>560436</v>
       </c>
       <c r="R20" t="n">
-        <v>6868997</v>
+        <v>6869040</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,6 +2614,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,15 +2646,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119299707</v>
+        <v>96362326</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2902,14 +2680,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>S Laxöringstjärnarna, Hls</t>
+          <t>Laxöringtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560194</v>
+        <v>560188</v>
       </c>
       <c r="R21" t="n">
-        <v>6869042</v>
+        <v>6868901</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,17 +2714,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Torrgran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,15 +2752,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119300124</v>
+        <v>96362551</v>
       </c>
       <c r="B22" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2990,21 +2763,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3013,14 +2786,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>S Laxöringstjärnarna, Hls</t>
+          <t>Laxöringtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560293</v>
+        <v>560378</v>
       </c>
       <c r="R22" t="n">
-        <v>6869024</v>
+        <v>6869127</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,17 +2820,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal tallåga.</t>
+          <t>Granbark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,43 +2858,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119299724</v>
+        <v>119299888</v>
       </c>
       <c r="B23" t="n">
-        <v>95202</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3129,10 +2896,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560196</v>
+        <v>560451</v>
       </c>
       <c r="R23" t="n">
-        <v>6869120</v>
+        <v>6869026</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,6 +2932,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Brandhögstubbe tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,15 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119299642</v>
+        <v>119300115</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3208,21 +2975,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3235,10 +3002,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560157</v>
+        <v>560275</v>
       </c>
       <c r="R24" t="n">
-        <v>6868939</v>
+        <v>6869039</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3275,7 +3042,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>På brandhögstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,62 +3070,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119299933</v>
+        <v>96362705</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>S Laxöringstjärnarna, Hls</t>
+          <t>Laxöringtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560389</v>
+        <v>560479</v>
       </c>
       <c r="R25" t="n">
-        <v>6869030</v>
+        <v>6869175</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3385,17 +3138,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>C:a &lt;  300 bladrosetter</t>
+          <t>Stenblock</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3423,62 +3176,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119299990</v>
+        <v>96362185</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>S Laxöringstjärnarna, Hls</t>
+          <t>Laxöringtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560305</v>
+        <v>560161</v>
       </c>
       <c r="R26" t="n">
-        <v>6869050</v>
+        <v>6869160</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3505,17 +3244,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>C.a 30 bladrosetter</t>
+          <t>Högstubbe.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3543,15 +3282,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119299792</v>
+        <v>119300107</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3559,21 +3293,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3586,10 +3320,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560436</v>
+        <v>560275</v>
       </c>
       <c r="R27" t="n">
-        <v>6869040</v>
+        <v>6869039</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3360,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På tallstam.</t>
+          <t>På högstubbe.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3654,37 +3388,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119299449</v>
+        <v>96362674</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3693,14 +3422,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>N Laxöringstjärnarna, Hls</t>
+          <t>Laxöringtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560067</v>
+        <v>560539</v>
       </c>
       <c r="R28" t="n">
-        <v>6868823</v>
+        <v>6869155</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3727,12 +3456,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera aspar i området är bevuxna med skinnlav.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3760,37 +3494,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119300157</v>
+        <v>119300062</v>
       </c>
       <c r="B29" t="n">
-        <v>78560</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3803,10 +3532,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560203</v>
+        <v>560283</v>
       </c>
       <c r="R29" t="n">
-        <v>6869100</v>
+        <v>6869053</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3839,6 +3568,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På aspstam.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3866,54 +3600,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119299746</v>
+        <v>96362340</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>S Laxöringstjärnarna, Hls</t>
+          <t>Laxöringtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560403</v>
+        <v>560270</v>
       </c>
       <c r="R30" t="n">
-        <v>6869102</v>
+        <v>6869068</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3940,17 +3668,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>C:a 200 bladrosetter</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3978,62 +3706,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119299982</v>
+        <v>96362484</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>S Laxöringstjärnarna, Hls</t>
+          <t>Laxöringtjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560379</v>
+        <v>560319</v>
       </c>
       <c r="R31" t="n">
-        <v>6869016</v>
+        <v>6869102</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,17 +3774,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>C.a 60 bladrosetter.</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4101,12 +3815,7 @@
         <v>119299780</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4209,37 +3918,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119300062</v>
+        <v>119299968</v>
       </c>
       <c r="B33" t="n">
-        <v>79511</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4252,10 +3956,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560283</v>
+        <v>560384</v>
       </c>
       <c r="R33" t="n">
-        <v>6869053</v>
+        <v>6869021</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4292,7 +3996,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På aspstam.</t>
+          <t>På mkt gammal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4320,15 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119300107</v>
+        <v>119300082</v>
       </c>
       <c r="B34" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4336,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4363,10 +4062,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560275</v>
+        <v>560269</v>
       </c>
       <c r="R34" t="n">
-        <v>6869039</v>
+        <v>6869053</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4403,7 +4102,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På högstubbe.</t>
+          <t>Sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4431,15 +4130,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119299481</v>
+        <v>119299941</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4447,37 +4141,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N Laxöringstjärnarna, Hls</t>
+          <t>S Laxöringstjärnarna, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560077</v>
+        <v>560389</v>
       </c>
       <c r="R35" t="n">
-        <v>6868900</v>
+        <v>6869030</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,15 +4232,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119300016</v>
+        <v>119299746</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4570,17 +4260,9 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -4589,10 +4271,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560335</v>
+        <v>560403</v>
       </c>
       <c r="R36" t="n">
-        <v>6869047</v>
+        <v>6869102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4629,7 +4311,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>C.a 60 bladrosetter</t>
+          <t>C:a 200 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4660,12 +4342,7 @@
         <v>119299768</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,42 +4449,46 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119299733</v>
+        <v>119299933</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4815,10 +4496,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560426</v>
+        <v>560389</v>
       </c>
       <c r="R38" t="n">
-        <v>6869106</v>
+        <v>6869030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4855,7 +4536,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Tallstam</t>
+          <t>C:a &lt;  300 bladrosetter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4883,42 +4564,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119299902</v>
+        <v>119299982</v>
       </c>
       <c r="B39" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -4927,10 +4611,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560384</v>
+        <v>560379</v>
       </c>
       <c r="R39" t="n">
-        <v>6869038</v>
+        <v>6869016</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4963,6 +4647,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>C.a 60 bladrosetter.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4990,42 +4679,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119299505</v>
+        <v>119299990</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5033,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560084</v>
+        <v>560305</v>
       </c>
       <c r="R40" t="n">
-        <v>6868936</v>
+        <v>6869050</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5069,6 +4762,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>C.a 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5096,42 +4794,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119299894</v>
+        <v>119300016</v>
       </c>
       <c r="B41" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5139,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560442</v>
+        <v>560335</v>
       </c>
       <c r="R41" t="n">
-        <v>6869019</v>
+        <v>6869047</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5175,6 +4877,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>C.a 60 bladrosetter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5202,37 +4909,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119299688</v>
+        <v>119300035</v>
       </c>
       <c r="B42" t="n">
-        <v>95455</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5246,10 +4948,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560180</v>
+        <v>560298</v>
       </c>
       <c r="R42" t="n">
-        <v>6869037</v>
+        <v>6869055</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5286,7 +4988,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Gammal tallåga</t>
+          <t>Rikligt med bladrosetter c:a 1m2</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5314,42 +5016,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119300115</v>
+        <v>119300075</v>
       </c>
       <c r="B43" t="n">
-        <v>78262</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5357,10 +5055,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560275</v>
+        <v>560283</v>
       </c>
       <c r="R43" t="n">
-        <v>6869039</v>
+        <v>6869048</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5397,7 +5095,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På brandhögstubbe</t>
+          <t>Rikligt med bladrosetter c:a 1m2</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5422,6 +5120,316 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>119299739</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>S Laxöringstjärnarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>560408</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6869105</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>119299902</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>S Laxöringstjärnarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>560384</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6869038</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>96362203</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Laxöringtjärnarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>560115</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6869110</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spridd i området på tall o gran.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23984-2022 artfynd.xlsx
+++ b/artfynd/A 23984-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299688</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362520</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300157</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299449</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362564</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97495431</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362720</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1612,6 +1657,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300124</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299724</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362269</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299481</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299505</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2118,6 +2188,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299528</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299658</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2325,6 +2405,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299642</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2431,6 +2516,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299707</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2537,6 +2627,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299733</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2643,6 +2738,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299792</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2749,6 +2849,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362326</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2855,6 +2960,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362551</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2961,6 +3071,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299888</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3067,6 +3182,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300115</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3173,6 +3293,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362705</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3279,6 +3404,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362185</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3385,6 +3515,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300107</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3491,6 +3626,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362674</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3597,6 +3737,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300062</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3703,6 +3848,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362340</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3809,6 +3959,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362484</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3915,6 +4070,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299780</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4021,6 +4181,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299968</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4127,6 +4292,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300082</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4229,6 +4399,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299941</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4336,6 +4511,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299746</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4446,6 +4626,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299768</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4561,6 +4746,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299933</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4676,6 +4866,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299982</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4791,6 +4986,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299990</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4906,6 +5106,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300016</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5013,6 +5218,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300035</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5120,6 +5330,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119300075</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5222,6 +5437,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299739</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5324,6 +5544,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119299902</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5430,8 +5655,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96362203</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>